--- a/快手作品数据.xlsx
+++ b/快手作品数据.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>483</v>
+        <v>560</v>
       </c>
       <c r="D9" t="n">
         <v>15.2</v>
@@ -872,25 +872,71 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>首镜弱：2s跳出26.7%、官方提示第1-4秒跳出56%=开场炸点失效；完播6.2%；时长51.1s偏长</t>
+          <t>首镜弱：2s跳出26.7%、官方提示第1-4秒跳出56%=开场炸点失效；完播6.2%；时长51.1s偏长 | 9/28更新:560播放/赞9/藏1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>山海经·饕餮</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-27 20:00</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>153</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>无助推（20h早期数据）</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>首镜教训第3例：官方提示第1-2秒跳出55%；2s跳出24.6%落入危险区；完播3.5%；羊身人面设定猎奇但首帧冲击不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>糖画匠(老手艺)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-09-15 22:59</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>3026</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>截图批次漏掉的一条；9/24后台核对</t>
         </is>
@@ -1063,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2896,6 +2942,137 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>后台API采集</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>山海经·饕餮</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>播放量</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>153</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>后台采集(20h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>山海经·饕餮</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2秒跳出率</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>后台采集(20h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>山海经·饕餮</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5秒完播率</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>45.6%</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>后台采集(20h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>山海经·饕餮</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>完播率</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>后台采集(20h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>山海经·应龙</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>播放量</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>560</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>后台采集</t>
         </is>
       </c>
     </row>

--- a/快手作品数据.xlsx
+++ b/快手作品数据.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -939,6 +939,98 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>截图批次漏掉的一条；9/24后台核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>43</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>助推162次播放；9/30采(29h)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>★首镜决定论第4例：2s跳出51.8%全系列最差；官方提示第1-2秒跳出37%；首镜=乌云+翼虎俯冲剪影(单元素灰暗调)→次日播放+0热死极快；完播1.7%；标题分43（「帮坏人吃好人的怪兽」抽象概念开头）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-29 19:00</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>406</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>49</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>助推102次播放；9/30采(发布5h)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>★首镜决定论第5例：2s跳出31.5%&gt;20%线；首镜=暗殿凿子抵兽身(小场景暗调)；标题「被两个天帝…」概念开头违反公式→标题分49；完播1.1%；末镜预告夸父正常</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3073,6 +3165,582 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>后台采集</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>播放量</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>平均播放时长(秒)</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2秒跳出率</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>51.8%</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>5秒完播率</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19.7%</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>完播率</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>涨粉</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>标题分</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>43</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>流量助推</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>+162播放(画质/标题/内容超90%作者)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>山海经·穷奇</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>官方留存提示</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>第1→2秒跳出37%占比高</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>播放量</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>406</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>平均播放时长(秒)</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2秒跳出率</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>31.5%</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5秒完播率</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>36.7%</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>完播率</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>标题分</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>49</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>山海经·混沌</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>流量助推</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>+102播放(画质/标题/内容超90%作者)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>山海经·梼杌</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>发布状态</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>定时2026-09-30 19:00待发布(标题=老虎当猎物的上古凶兽，与史册同名)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>账号</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>近7日播放量</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>8934</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>后台登录核对(前日+993)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>账号</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>完播率(近7日)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>账号</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>净增粉丝(近7日)</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>17</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>账号</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>点赞/评论/分享(近7日)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>57/16/1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>账号</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>最新评论</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>09.29喃喃小语：这视频太真实了(已由作者首评回复)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>后台登录核对</t>
         </is>
       </c>
     </row>
